--- a/data/trans_bre/P57GLOBAL_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P57GLOBAL_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 6,97</t>
+          <t>-0,2; 6,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 8,47</t>
+          <t>1,1; 8,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 9,59</t>
+          <t>2,48; 9,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 9,52</t>
+          <t>-0,63; 8,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 9,39</t>
+          <t>-0,21; 9,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 12,21</t>
+          <t>1,48; 11,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 12,05</t>
+          <t>3,0; 12,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 15,03</t>
+          <t>-0,88; 13,95</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 4,31</t>
+          <t>-2,3; 4,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,26; 11,52</t>
+          <t>5,4; 11,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,02</t>
+          <t>-0,16; 4,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 22,12</t>
+          <t>-3,97; 22,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 6,52</t>
+          <t>-3,33; 6,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 17,55</t>
+          <t>7,92; 17,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 6,16</t>
+          <t>-0,19; 5,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 52,66</t>
+          <t>-6,32; 55,26</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,85; 1,88</t>
+          <t>-10,24; 1,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 6,89</t>
+          <t>-6,45; 6,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 4,7</t>
+          <t>-5,97; 4,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 0,91</t>
+          <t>-9,34; 1,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 3,02</t>
+          <t>-14,17; 2,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 10,85</t>
+          <t>-9,2; 9,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 6,19</t>
+          <t>-7,5; 5,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 1,59</t>
+          <t>-14,5; 2,73</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 4,04</t>
+          <t>-0,39; 3,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,32; 8,68</t>
+          <t>4,13; 8,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,8</t>
+          <t>1,08; 4,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 18,14</t>
+          <t>-1,84; 17,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,87</t>
+          <t>-0,54; 5,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,83</t>
+          <t>5,77; 12,54</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,95</t>
+          <t>1,29; 5,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 40,24</t>
+          <t>-2,99; 37,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57GLOBAL_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P57GLOBAL_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 6,82</t>
+          <t>0,17; 6,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,25</t>
+          <t>0,59; 8,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 9,56</t>
+          <t>2,67; 9,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 8,77</t>
+          <t>0,38; 9,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 9,39</t>
+          <t>0,26; 9,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 11,85</t>
+          <t>0,74; 11,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 12,08</t>
+          <t>3,2; 11,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 13,95</t>
+          <t>0,6; 13,91</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,33</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 4,03</t>
+          <t>-2,14; 4,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,51</t>
+          <t>5,19; 11,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 4,72</t>
+          <t>0,16; 4,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 22,08</t>
+          <t>-2,04; 4,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 6,12</t>
+          <t>-3,1; 6,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,92; 17,75</t>
+          <t>7,69; 17,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 5,77</t>
+          <t>0,19; 5,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 55,26</t>
+          <t>-3,08; 7,06</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,15</t>
+          <t>-4,19</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-6,81%</t>
+          <t>-6,77%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 1,9</t>
+          <t>-9,84; 2,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 6,34</t>
+          <t>-6,68; 6,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 4,24</t>
+          <t>-6,38; 4,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 1,56</t>
+          <t>-9,38; 1,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,17; 2,79</t>
+          <t>-13,96; 3,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 9,93</t>
+          <t>-9,57; 10,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 5,73</t>
+          <t>-8,09; 5,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 2,73</t>
+          <t>-14,53; 3,08</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 3,91</t>
+          <t>-0,48; 4,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 8,49</t>
+          <t>4,02; 8,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 4,69</t>
+          <t>1,09; 4,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 17,53</t>
+          <t>-1,3; 3,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 5,68</t>
+          <t>-0,68; 5,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 12,54</t>
+          <t>5,74; 12,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,81</t>
+          <t>1,32; 5,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 37,63</t>
+          <t>-2,0; 5,84</t>
         </is>
       </c>
     </row>
